--- a/Bosquejo de entidades..xlsx
+++ b/Bosquejo de entidades..xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbjl8\OneDrive\Escritorio\c#\ProyectoIntegrador\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79C285C8-277D-42DE-B9DA-08EE677B163F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AC86065-0433-4DA2-BF2E-06B602E0AC27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{68E3ABBE-551F-42E9-A2D4-74F9B47131F6}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="57">
   <si>
     <t>Producto</t>
   </si>
@@ -35,9 +35,6 @@
     <t>Solicitud de compra</t>
   </si>
   <si>
-    <t>1:N</t>
-  </si>
-  <si>
     <t>Id</t>
   </si>
   <si>
@@ -86,39 +83,12 @@
     <t>Subtotal</t>
   </si>
   <si>
-    <t>Colaborador</t>
-  </si>
-  <si>
-    <t>IdColaborador</t>
-  </si>
-  <si>
-    <t>Nombre</t>
-  </si>
-  <si>
-    <t>ApellidoPaterno</t>
-  </si>
-  <si>
-    <t>ApellidoMaterno</t>
-  </si>
-  <si>
-    <t>1 : 1</t>
-  </si>
-  <si>
     <t>José</t>
   </si>
   <si>
     <t>Productos</t>
   </si>
   <si>
-    <t>Zapatos</t>
-  </si>
-  <si>
-    <t>Tenis</t>
-  </si>
-  <si>
-    <t>Sandalias</t>
-  </si>
-  <si>
     <t>Borrador</t>
   </si>
   <si>
@@ -179,9 +149,6 @@
     <t>En espera de autorización</t>
   </si>
   <si>
-    <t>Zandalias</t>
-  </si>
-  <si>
     <t>Editar</t>
   </si>
   <si>
@@ -191,18 +158,6 @@
     <t>Problemas</t>
   </si>
   <si>
-    <t>Fuentes</t>
-  </si>
-  <si>
-    <t>Herramientas Utilizadas</t>
-  </si>
-  <si>
-    <t>Pendientes</t>
-  </si>
-  <si>
-    <t>Eliminación lógica para mantener el historial de registros de solicitudes como productos que se solicitaron.</t>
-  </si>
-  <si>
     <t>Antoni</t>
   </si>
   <si>
@@ -219,6 +174,30 @@
   </si>
   <si>
     <t xml:space="preserve">CodigoSolicitud =1 </t>
+  </si>
+  <si>
+    <t>Dudas</t>
+  </si>
+  <si>
+    <t>En las plantillas de las entidades se utilizan los metodos de acceso o solo se dejan las propiedades publicas?</t>
+  </si>
+  <si>
+    <t>Eliminación lógica para mantener el historial de registros de solicitudes y productos que se solicitaron.</t>
+  </si>
+  <si>
+    <t>Producto 1</t>
+  </si>
+  <si>
+    <t>Producto 2</t>
+  </si>
+  <si>
+    <t>Producto 3</t>
+  </si>
+  <si>
+    <t>Produco 3</t>
+  </si>
+  <si>
+    <t>No debe permitir agregarlo.</t>
   </si>
 </sst>
 </file>
@@ -250,7 +229,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -275,8 +254,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="28">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -437,97 +422,12 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -551,17 +451,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -585,6 +474,19 @@
         <color indexed="64"/>
       </top>
       <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -593,7 +495,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -646,99 +548,107 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -763,13 +673,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -821,13 +731,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>209550</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -890,13 +800,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>209550</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -948,13 +858,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>209550</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1006,13 +916,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>209550</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1064,13 +974,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>209550</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1122,13 +1032,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>209550</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1180,13 +1090,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>209550</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1238,13 +1148,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>209550</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1300,13 +1210,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1358,13 +1268,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1416,13 +1326,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>209550</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1474,13 +1384,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1532,13 +1442,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1590,13 +1500,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1648,13 +1558,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1706,13 +1616,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1764,13 +1674,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>209550</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1805,238 +1715,6 @@
         </a:effectRef>
         <a:fontRef idx="minor">
           <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="es-MX" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="31" name="Elipse 30">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8865746B-F3EF-4DCA-9F26-5BDB52575F9C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="819150" y="3105150"/>
-          <a:ext cx="142875" cy="85725"/>
-        </a:xfrm>
-        <a:prstGeom prst="ellipse">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="3">
-          <a:schemeClr val="lt1"/>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent6"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent6"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="es-MX" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>209550</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="32" name="Elipse 31">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74BC23F9-736B-449D-97B2-285D8BF23A68}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="828675" y="819150"/>
-          <a:ext cx="142875" cy="85725"/>
-        </a:xfrm>
-        <a:prstGeom prst="ellipse">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent6"/>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="lt1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent6"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="es-MX" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>209550</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="33" name="Elipse 32">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E60F68E-4FF8-4B17-8899-2299EC21FDFF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="828675" y="3676650"/>
-          <a:ext cx="142875" cy="85725"/>
-        </a:xfrm>
-        <a:prstGeom prst="ellipse">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent6"/>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="lt1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent6"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="es-MX" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>209550</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="38" name="Elipse 37">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A357F78-8578-4417-B43F-77D9DB106595}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="828675" y="1009650"/>
-          <a:ext cx="142875" cy="85725"/>
-        </a:xfrm>
-        <a:prstGeom prst="ellipse">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent6"/>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="lt1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent6"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
@@ -2155,65 +1833,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>409575</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="48" name="Conector recto 47">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78DBCD90-0F95-5306-8499-A72DD81D4906}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="409575" y="685800"/>
-          <a:ext cx="9525" cy="2305050"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1686719</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>99219</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>109141</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -2260,13 +1888,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>99218</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>109140</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -2395,8 +2023,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="8056563" y="615156"/>
-          <a:ext cx="2441048" cy="3248025"/>
+          <a:off x="7099749" y="611705"/>
+          <a:ext cx="2458591" cy="3231057"/>
           <a:chOff x="9423004" y="198437"/>
           <a:chExt cx="2655491" cy="3297635"/>
         </a:xfrm>
@@ -3309,491 +2937,497 @@
   <dimension ref="A2:M42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="4.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.453125" customWidth="1"/>
-    <col min="3" max="3" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.81640625" customWidth="1"/>
+    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.81640625" customWidth="1"/>
+    <col min="5" max="5" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.81640625" customWidth="1"/>
+    <col min="8" max="8" width="17.453125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.453125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="8" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="8.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="J2" s="46" t="s">
-        <v>41</v>
-      </c>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46"/>
-      <c r="M2" s="46"/>
+      <c r="A2" s="6"/>
+      <c r="B2" s="49" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="J2" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" s="36"/>
+      <c r="L2" s="36"/>
+      <c r="M2" s="36"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="B3" s="2"/>
+      <c r="B3" s="48"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="B4" s="3" t="s">
-        <v>20</v>
+      <c r="A4" s="5"/>
+      <c r="B4" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="1"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="B5" s="3" t="s">
-        <v>21</v>
-      </c>
+      <c r="A5" s="47"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="56"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="2"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A6" s="47"/>
       <c r="B6" s="3" t="s">
-        <v>22</v>
+        <v>2</v>
+      </c>
+      <c r="D6" s="59"/>
+      <c r="E6" s="60"/>
+      <c r="F6" s="61"/>
+      <c r="H6" s="4" t="s">
+        <v>2</v>
       </c>
       <c r="L6" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A7" s="47"/>
       <c r="B7" s="3" t="s">
-        <v>23</v>
+        <v>8</v>
+      </c>
+      <c r="D7" s="58" t="s">
+        <v>2</v>
+      </c>
+      <c r="E7" s="58"/>
+      <c r="F7" s="58"/>
+      <c r="H7" s="4" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A8" s="47"/>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="H8" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="M8" t="s">
-        <v>51</v>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="B9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="H9" s="4" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A10" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="1"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>0</v>
+      <c r="B10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="37"/>
+      <c r="F10" s="37"/>
+      <c r="H10" s="4" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="B11" s="2"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="50" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" s="51"/>
-      <c r="F11" s="52"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="2"/>
+      <c r="B11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="37"/>
+      <c r="F11" s="37"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="37"/>
+      <c r="F12" s="37"/>
+      <c r="J12" t="s">
+        <v>29</v>
+      </c>
+      <c r="M12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B15" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="51"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="51"/>
+      <c r="F15" s="51"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="51"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="B16" s="24"/>
+      <c r="G16" s="47"/>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B17" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="52"/>
+      <c r="F17" s="53"/>
+      <c r="G17" s="47"/>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B18" s="2">
+        <v>1</v>
+      </c>
+      <c r="C18" s="2">
+        <v>1001</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" s="2">
+        <v>100</v>
+      </c>
+      <c r="F18" s="2">
+        <v>1</v>
+      </c>
+      <c r="G18" s="47"/>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B19" s="2">
+        <v>2</v>
+      </c>
+      <c r="C19" s="2">
+        <v>1002</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E19" s="2">
+        <v>90</v>
+      </c>
+      <c r="F19" s="2">
+        <v>1</v>
+      </c>
+      <c r="G19" s="47"/>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B20" s="2">
         <v>3</v>
       </c>
-      <c r="D12" s="53"/>
-      <c r="E12" s="53"/>
-      <c r="F12" s="53"/>
-      <c r="H12" s="4" t="s">
+      <c r="C20" s="2">
+        <v>1003</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20" s="2">
+        <v>70</v>
+      </c>
+      <c r="F20" s="2">
+        <v>1</v>
+      </c>
+      <c r="G20" s="47"/>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B21" s="47"/>
+      <c r="G21" s="47"/>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B22" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="52"/>
+      <c r="D22" s="52"/>
+      <c r="E22" s="52"/>
+      <c r="F22" s="52"/>
+      <c r="G22" s="52"/>
+      <c r="H22" s="52"/>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B23" s="54">
+        <v>1</v>
+      </c>
+      <c r="C23" s="2">
+        <v>1</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="23">
+        <v>46241</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H23" s="2">
+        <f>SUM(G28:G30)</f>
+        <v>540</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B24" s="54">
+        <v>2</v>
+      </c>
+      <c r="C24" s="2">
+        <v>2</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E24" s="23">
+        <v>46241</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H24" s="2">
+        <f>SUM(G31:G32)</f>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B25" s="54">
         <v>3</v>
       </c>
-      <c r="J12" t="s">
-        <v>39</v>
-      </c>
-      <c r="M12" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="B13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="53" t="s">
+      <c r="C25" s="2">
         <v>3</v>
       </c>
-      <c r="E13" s="53"/>
-      <c r="F13" s="53"/>
-      <c r="H13" s="4" t="s">
+      <c r="D25" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="23">
+        <v>46241</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H25" s="2">
+        <f>G33</f>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B26" s="47"/>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B27" s="52" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" s="52"/>
+      <c r="D27" s="52"/>
+      <c r="E27" s="52"/>
+      <c r="F27" s="52"/>
+      <c r="G27" s="52"/>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B28" s="54">
+        <v>1</v>
+      </c>
+      <c r="C28" s="2">
+        <v>1</v>
+      </c>
+      <c r="D28" s="2">
+        <v>1</v>
+      </c>
+      <c r="E28" s="2">
+        <v>2</v>
+      </c>
+      <c r="F28" s="2">
+        <v>100</v>
+      </c>
+      <c r="G28" s="2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B29" s="54">
+        <v>2</v>
+      </c>
+      <c r="C29" s="2">
+        <v>1</v>
+      </c>
+      <c r="D29" s="2">
+        <v>2</v>
+      </c>
+      <c r="E29" s="2">
+        <v>3</v>
+      </c>
+      <c r="F29" s="2">
+        <v>90</v>
+      </c>
+      <c r="G29" s="2">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B30" s="54">
+        <v>3</v>
+      </c>
+      <c r="C30" s="2">
+        <v>1</v>
+      </c>
+      <c r="D30" s="2">
+        <v>3</v>
+      </c>
+      <c r="E30" s="2">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2">
+        <v>70</v>
+      </c>
+      <c r="G30" s="2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B31" s="54">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="B14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" s="53" t="s">
-        <v>16</v>
-      </c>
-      <c r="E14" s="53"/>
-      <c r="F14" s="53"/>
-      <c r="H14" s="4" t="s">
+      <c r="C31" s="2">
+        <v>2</v>
+      </c>
+      <c r="D31" s="2">
+        <v>1</v>
+      </c>
+      <c r="E31" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="B15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="E15" s="53"/>
-      <c r="F15" s="53"/>
-      <c r="H15" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="B16" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="E16" s="53"/>
-      <c r="F16" s="53"/>
-      <c r="H16" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B17" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="53" t="s">
+      <c r="F31" s="2">
+        <v>100</v>
+      </c>
+      <c r="G31" s="2">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B32" s="54">
+        <v>5</v>
+      </c>
+      <c r="C32" s="2">
+        <v>2</v>
+      </c>
+      <c r="D32" s="2">
+        <v>2</v>
+      </c>
+      <c r="E32" s="2">
+        <v>5</v>
+      </c>
+      <c r="F32" s="2">
+        <v>90</v>
+      </c>
+      <c r="G32" s="2">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B33" s="54">
         <v>6</v>
       </c>
-      <c r="E17" s="53"/>
-      <c r="F17" s="53"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B18" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D18" s="53" t="s">
-        <v>18</v>
-      </c>
-      <c r="E18" s="53"/>
-      <c r="F18" s="53"/>
-    </row>
-    <row r="20" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="21" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="43" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" s="44"/>
-      <c r="C21" s="44"/>
-      <c r="D21" s="44"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="45"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="24"/>
-      <c r="F22" s="25"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="24"/>
-      <c r="F23" s="25"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="47" t="s">
-        <v>26</v>
-      </c>
-      <c r="B24" s="48"/>
-      <c r="C24" s="48"/>
-      <c r="D24" s="49"/>
-      <c r="F24" s="25"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="26">
-        <v>1</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C25" s="2">
-        <v>100</v>
-      </c>
-      <c r="D25" s="2">
-        <v>1</v>
-      </c>
-      <c r="F25" s="25"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="26">
+      <c r="C33" s="2">
+        <v>3</v>
+      </c>
+      <c r="D33" s="2">
         <v>2</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C26" s="2">
-        <v>90</v>
-      </c>
-      <c r="D26" s="2">
-        <v>1</v>
-      </c>
-      <c r="F26" s="25"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="26">
-        <v>3</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C27" s="2">
+      <c r="E33" s="2">
+        <v>2</v>
+      </c>
+      <c r="F33" s="2">
         <v>70</v>
       </c>
-      <c r="D27" s="2">
-        <v>1</v>
-      </c>
-      <c r="F27" s="25"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" s="24"/>
-      <c r="F28" s="25"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="B29" s="41"/>
-      <c r="C29" s="41"/>
-      <c r="D29" s="41"/>
-      <c r="E29" s="41"/>
-      <c r="F29" s="42"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" s="26">
-        <v>1</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C30" s="23">
-        <v>46241</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F30" s="27">
-        <f>SUM(E35:E37)</f>
-        <v>540</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" s="26">
-        <v>2</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C31" s="23">
-        <v>46241</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F31" s="27">
-        <f>SUM(E38:E39)</f>
-        <v>950</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" s="26">
-        <v>3</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C32" s="23">
-        <v>46241</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F32" s="27">
-        <f>E40</f>
+      <c r="G33" s="2">
         <v>140</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" s="24"/>
-      <c r="F33" s="25"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="B34" s="48"/>
-      <c r="C34" s="48"/>
-      <c r="D34" s="48"/>
-      <c r="E34" s="49"/>
-      <c r="F34" s="25"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A35" s="26">
-        <v>1</v>
-      </c>
-      <c r="B35" s="2">
-        <v>1</v>
-      </c>
-      <c r="C35" s="2">
-        <v>2</v>
-      </c>
-      <c r="D35" s="2">
-        <v>100</v>
-      </c>
-      <c r="E35" s="2">
-        <v>200</v>
-      </c>
-      <c r="F35" s="25"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A36" s="26">
-        <v>1</v>
-      </c>
-      <c r="B36" s="2">
-        <v>2</v>
-      </c>
-      <c r="C36" s="2">
-        <v>3</v>
-      </c>
-      <c r="D36" s="2">
-        <v>90</v>
-      </c>
-      <c r="E36" s="2">
-        <v>270</v>
-      </c>
-      <c r="F36" s="25"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A37" s="26">
-        <v>1</v>
-      </c>
-      <c r="B37" s="2">
-        <v>3</v>
-      </c>
-      <c r="C37" s="2">
-        <v>1</v>
-      </c>
-      <c r="D37" s="2">
-        <v>70</v>
-      </c>
-      <c r="E37" s="2">
-        <v>70</v>
-      </c>
-      <c r="F37" s="25"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" s="26">
-        <v>2</v>
-      </c>
-      <c r="B38" s="2">
-        <v>1</v>
-      </c>
-      <c r="C38" s="2">
-        <v>5</v>
-      </c>
-      <c r="D38" s="2">
-        <v>100</v>
-      </c>
-      <c r="E38" s="2">
-        <v>500</v>
-      </c>
-      <c r="F38" s="25"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A39" s="26">
-        <v>2</v>
-      </c>
-      <c r="B39" s="2">
-        <v>2</v>
-      </c>
-      <c r="C39" s="2">
-        <v>5</v>
-      </c>
-      <c r="D39" s="2">
-        <v>90</v>
-      </c>
-      <c r="E39" s="2">
-        <v>450</v>
-      </c>
-      <c r="F39" s="25"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A40" s="26">
-        <v>3</v>
-      </c>
-      <c r="B40" s="2">
-        <v>2</v>
-      </c>
-      <c r="C40" s="2">
-        <v>2</v>
-      </c>
-      <c r="D40" s="2">
-        <v>70</v>
-      </c>
-      <c r="E40" s="2">
-        <v>140</v>
-      </c>
-      <c r="F40" s="25"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F40" s="47"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="24"/>
-      <c r="F41" s="25"/>
-    </row>
-    <row r="42" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="28"/>
-      <c r="B42" s="29"/>
-      <c r="C42" s="29"/>
-      <c r="D42" s="29"/>
-      <c r="E42" s="29"/>
-      <c r="F42" s="30"/>
+      <c r="F41" s="47"/>
+    </row>
+    <row r="42" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="25"/>
+      <c r="B42" s="26"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="47"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A21:F21"/>
+  <mergeCells count="13">
+    <mergeCell ref="B15:H15"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B22:H22"/>
+    <mergeCell ref="B27:G27"/>
     <mergeCell ref="J2:M2"/>
-    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D10:F10"/>
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="D12:F12"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="D5:F5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3818,20 +3452,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="56"/>
-      <c r="I2" s="57" t="s">
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="40"/>
+      <c r="I2" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="J2" s="58"/>
-      <c r="K2" s="58"/>
-      <c r="L2" s="59"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="43"/>
     </row>
     <row r="3" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B3" s="9"/>
@@ -3841,40 +3475,40 @@
       <c r="F3" s="15"/>
       <c r="G3" s="10"/>
       <c r="I3" s="17" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="J3" s="18" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K3" s="18" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="L3" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B4" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" s="31" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>8</v>
       </c>
       <c r="D4" s="4">
         <v>1</v>
       </c>
-      <c r="E4" s="32" t="s">
-        <v>12</v>
+      <c r="E4" s="28" t="s">
+        <v>11</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G4" s="10"/>
       <c r="I4" s="20">
         <v>1001</v>
       </c>
       <c r="J4" s="21" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="K4" s="21">
         <v>100</v>
@@ -3885,29 +3519,29 @@
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B5" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C5" s="33" t="s">
-        <v>10</v>
+        <v>34</v>
+      </c>
+      <c r="C5" s="29" t="s">
+        <v>9</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" s="34" t="s">
-        <v>42</v>
+        <v>38</v>
+      </c>
+      <c r="E5" s="30" t="s">
+        <v>32</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="G5" s="10"/>
       <c r="I5" s="14">
         <v>1002</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="K5" s="15">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="L5" s="16">
         <v>1</v>
@@ -3915,28 +3549,28 @@
     </row>
     <row r="6" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B6" s="9"/>
-      <c r="C6" s="35" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="37">
+      <c r="C6" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="33">
         <v>46242</v>
       </c>
-      <c r="E6" s="36" t="s">
-        <v>14</v>
+      <c r="E6" s="32" t="s">
+        <v>13</v>
       </c>
       <c r="F6" s="4">
         <f>SUM(F12:F25)</f>
-        <v>800</v>
+        <v>1050</v>
       </c>
       <c r="G6" s="10"/>
       <c r="I6" s="17">
         <v>1003</v>
       </c>
       <c r="J6" s="18" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="K6" s="18">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="L6" s="19">
         <v>1</v>
@@ -3948,18 +3582,18 @@
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B8" s="9"/>
-      <c r="C8" s="54" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="55"/>
-      <c r="E8" s="55"/>
-      <c r="F8" s="56"/>
+      <c r="C8" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="39"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="40"/>
       <c r="G8" s="10"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B9" s="9"/>
       <c r="C9" s="9" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="F9" s="10"/>
       <c r="G9" s="10"/>
@@ -3970,26 +3604,26 @@
       <c r="F10" s="10"/>
       <c r="G10" s="10"/>
       <c r="I10" s="15" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B11" s="9"/>
-      <c r="C11" s="38" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" s="38" t="s">
+      <c r="C11" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" s="35" t="s">
         <v>17</v>
-      </c>
-      <c r="E11" s="38" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" s="39" t="s">
-        <v>18</v>
       </c>
       <c r="G11" s="10"/>
       <c r="I11" s="15" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.35">
@@ -4011,7 +3645,7 @@
       </c>
       <c r="G12" s="10"/>
       <c r="I12" s="15" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.35">
@@ -4024,39 +3658,42 @@
       </c>
       <c r="E13" s="15">
         <f>VLOOKUP(C13,I$4:$L$6,3,0)</f>
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F13" s="16">
         <f t="shared" ref="F13:F14" si="0">D13*E13</f>
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="G13" s="10"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B14" s="9"/>
-      <c r="C14" s="14">
+      <c r="C14" s="44">
         <v>1001</v>
       </c>
-      <c r="D14" s="15">
-        <v>2</v>
-      </c>
-      <c r="E14" s="15">
+      <c r="D14" s="45">
+        <v>5</v>
+      </c>
+      <c r="E14" s="45">
         <f>VLOOKUP(C14,I$4:$L$6,3,0)</f>
         <v>100</v>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="46">
         <f t="shared" si="0"/>
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="G14" s="10"/>
+      <c r="H14" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B15" s="9"/>
       <c r="C15" s="14"/>
       <c r="D15" s="15"/>
-      <c r="E15" s="15" t="e">
-        <f>VLOOKUP(C15,I$4:$L$6,3,0)</f>
-        <v>#N/A</v>
+      <c r="E15" s="15">
+        <f>IFERROR((VLOOKUP(C15,I$4:$L$6,3,0)),0)</f>
+        <v>0</v>
       </c>
       <c r="F15" s="16">
         <f>IFERROR(D15*E15,0)</f>
@@ -4068,9 +3705,9 @@
       <c r="B16" s="9"/>
       <c r="C16" s="14"/>
       <c r="D16" s="15"/>
-      <c r="E16" s="15" t="e">
-        <f>VLOOKUP(C16,I$4:$L$6,3,0)</f>
-        <v>#N/A</v>
+      <c r="E16" s="15">
+        <f>IFERROR((VLOOKUP(C16,I$4:$L$6,3,0)),0)</f>
+        <v>0</v>
       </c>
       <c r="F16" s="16">
         <f t="shared" ref="F16:F25" si="1">IFERROR(D16*E16,0)</f>
@@ -4082,9 +3719,9 @@
       <c r="B17" s="9"/>
       <c r="C17" s="14"/>
       <c r="D17" s="15"/>
-      <c r="E17" s="15" t="e">
-        <f>VLOOKUP(C17,I$4:$L$6,3,0)</f>
-        <v>#N/A</v>
+      <c r="E17" s="15">
+        <f>IFERROR((VLOOKUP(C17,I$4:$L$6,3,0)),0)</f>
+        <v>0</v>
       </c>
       <c r="F17" s="16">
         <f t="shared" si="1"/>
@@ -4096,9 +3733,9 @@
       <c r="B18" s="9"/>
       <c r="C18" s="14"/>
       <c r="D18" s="15"/>
-      <c r="E18" s="15" t="e">
-        <f>VLOOKUP(C18,I$4:$L$6,3,0)</f>
-        <v>#N/A</v>
+      <c r="E18" s="15">
+        <f>IFERROR((VLOOKUP(C18,I$4:$L$6,3,0)),0)</f>
+        <v>0</v>
       </c>
       <c r="F18" s="16">
         <f t="shared" si="1"/>
@@ -4110,9 +3747,9 @@
       <c r="B19" s="9"/>
       <c r="C19" s="14"/>
       <c r="D19" s="15"/>
-      <c r="E19" s="15" t="e">
-        <f>VLOOKUP(C19,I$4:$L$6,3,0)</f>
-        <v>#N/A</v>
+      <c r="E19" s="15">
+        <f>IFERROR((VLOOKUP(C19,I$4:$L$6,3,0)),0)</f>
+        <v>0</v>
       </c>
       <c r="F19" s="16">
         <f t="shared" si="1"/>
@@ -4124,9 +3761,9 @@
       <c r="B20" s="9"/>
       <c r="C20" s="14"/>
       <c r="D20" s="15"/>
-      <c r="E20" s="15" t="e">
-        <f>VLOOKUP(C20,I$4:$L$6,3,0)</f>
-        <v>#N/A</v>
+      <c r="E20" s="15">
+        <f>IFERROR((VLOOKUP(C20,I$4:$L$6,3,0)),0)</f>
+        <v>0</v>
       </c>
       <c r="F20" s="16">
         <f t="shared" si="1"/>
@@ -4138,9 +3775,9 @@
       <c r="B21" s="9"/>
       <c r="C21" s="14"/>
       <c r="D21" s="15"/>
-      <c r="E21" s="15" t="e">
-        <f>VLOOKUP(C21,I$4:$L$6,3,0)</f>
-        <v>#N/A</v>
+      <c r="E21" s="15">
+        <f>IFERROR((VLOOKUP(C21,I$4:$L$6,3,0)),0)</f>
+        <v>0</v>
       </c>
       <c r="F21" s="16">
         <f t="shared" si="1"/>
@@ -4152,9 +3789,9 @@
       <c r="B22" s="9"/>
       <c r="C22" s="14"/>
       <c r="D22" s="15"/>
-      <c r="E22" s="15" t="e">
-        <f>VLOOKUP(C22,I$4:$L$6,3,0)</f>
-        <v>#N/A</v>
+      <c r="E22" s="15">
+        <f>IFERROR((VLOOKUP(C22,I$4:$L$6,3,0)),0)</f>
+        <v>0</v>
       </c>
       <c r="F22" s="16">
         <f t="shared" si="1"/>
@@ -4166,9 +3803,9 @@
       <c r="B23" s="9"/>
       <c r="C23" s="14"/>
       <c r="D23" s="15"/>
-      <c r="E23" s="15" t="e">
-        <f>VLOOKUP(C23,I$4:$L$6,3,0)</f>
-        <v>#N/A</v>
+      <c r="E23" s="15">
+        <f>IFERROR((VLOOKUP(C23,I$4:$L$6,3,0)),0)</f>
+        <v>0</v>
       </c>
       <c r="F23" s="16">
         <f t="shared" si="1"/>
@@ -4180,9 +3817,9 @@
       <c r="B24" s="9"/>
       <c r="C24" s="14"/>
       <c r="D24" s="15"/>
-      <c r="E24" s="15" t="e">
-        <f>VLOOKUP(C24,I$4:$L$6,3,0)</f>
-        <v>#N/A</v>
+      <c r="E24" s="15">
+        <f>IFERROR((VLOOKUP(C24,I$4:$L$6,3,0)),0)</f>
+        <v>0</v>
       </c>
       <c r="F24" s="16">
         <f t="shared" si="1"/>
@@ -4194,11 +3831,11 @@
       <c r="B25" s="9"/>
       <c r="C25" s="17"/>
       <c r="D25" s="18"/>
-      <c r="E25" s="18" t="e">
-        <f>VLOOKUP(C25,I$4:$L$6,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F25" s="16">
+      <c r="E25" s="18">
+        <f>IFERROR((VLOOKUP(C25,I$4:$L$6,3,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4214,17 +3851,17 @@
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.35">
       <c r="C29" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.35">
       <c r="C30" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.35">
       <c r="C31" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -4239,37 +3876,35 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA8548E4-0317-454C-9FCF-0A36B8E95F8C}">
-  <dimension ref="A1:A64"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="90.36328125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>52</v>
+      <c r="A1" s="30" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A10" s="30" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
-        <v>56</v>
+      <c r="A16" s="30" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
